--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F3F9D1-B638-4027-9C45-DB7D02964EE7}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D61130D-C6F0-4072-B5E4-3E21EDE3C918}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="168">
   <si>
     <t>PerkID</t>
   </si>
@@ -760,16 +760,25 @@
     </r>
   </si>
   <si>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>CritChance</t>
+  </si>
+  <si>
+    <t>CritDamage</t>
+  </si>
+  <si>
     <t>PlayerBaseStatID</t>
-  </si>
-  <si>
-    <t>AttackSpeed</t>
-  </si>
-  <si>
-    <t>CritChance</t>
-  </si>
-  <si>
-    <t>CritDamage</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RunSpeed</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1179,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80FDACC5-480A-45D9-990F-F547CEC76173}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1187,16 +1196,17 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>82</v>
@@ -1208,16 +1218,19 @@
         <v>84</v>
       </c>
       <c r="F1" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -1231,15 +1244,18 @@
         <v>5</v>
       </c>
       <c r="E2" s="14">
+        <v>2</v>
+      </c>
+      <c r="F2" s="14">
         <v>5</v>
       </c>
-      <c r="F2" s="14">
-        <v>0</v>
-      </c>
       <c r="G2" s="14">
+        <v>0</v>
+      </c>
+      <c r="H2" s="14">
         <v>5</v>
       </c>
-      <c r="H2" s="14">
+      <c r="I2" s="14">
         <v>150</v>
       </c>
     </row>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D61130D-C6F0-4072-B5E4-3E21EDE3C918}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FE3B6B-059D-4ACC-AECD-295DB57A9456}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -28,18 +28,14 @@
     <sheet name="DungeonRoomTable" sheetId="12" r:id="rId13"/>
     <sheet name="RoomSpawnTable" sheetId="13" r:id="rId14"/>
     <sheet name="EquipmentTable" sheetId="14" r:id="rId15"/>
+    <sheet name="ConsumableTable" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="187">
   <si>
     <t>PerkID</t>
   </si>
@@ -780,12 +776,120 @@
     <t>RunSpeed</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>ItemID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectValue</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconPath</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하급 물약</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>상급 물약</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>HP를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 30 회복한다.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>HP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 80 회복한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Potion_Low</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Potion_High</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Steel_Helmet</t>
+  </si>
+  <si>
+    <t>Icons/Leather_Armor</t>
+  </si>
+  <si>
+    <t>Icons/Swift_Boots</t>
+  </si>
+  <si>
+    <t>Icons/Power_Ring</t>
+  </si>
+  <si>
+    <t>Icons/Haste_Necklace</t>
+  </si>
+  <si>
+    <t>Icons/Guardian_Amulet</t>
+  </si>
+  <si>
+    <t>Icons/Slash_Bracelet</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -834,6 +938,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -879,10 +996,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -924,9 +1042,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{E96E5ABA-5D01-4D54-9142-2C1247B269A5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1762,7 +1884,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1770,9 +1892,10 @@
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>145</v>
       </c>
@@ -1794,8 +1917,11 @@
       <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -1817,8 +1943,11 @@
       <c r="G2" s="10" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -1840,8 +1969,11 @@
       <c r="G3" s="12" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="3">
         <v>1003</v>
       </c>
@@ -1863,8 +1995,11 @@
       <c r="G4" s="10" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="6">
         <v>1004</v>
       </c>
@@ -1886,8 +2021,11 @@
       <c r="G5" s="12" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="3">
         <v>1005</v>
       </c>
@@ -1909,8 +2047,11 @@
       <c r="G6" s="10" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="6">
         <v>1006</v>
       </c>
@@ -1932,8 +2073,11 @@
       <c r="G7" s="12" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="3">
         <v>1007</v>
       </c>
@@ -1954,12 +2098,94 @@
       </c>
       <c r="G8" s="10" t="s">
         <v>161</v>
+      </c>
+      <c r="H8" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6712144-EE6D-453D-A942-3F286BAEA58E}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3">
+        <v>2001</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>30</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="6">
+        <v>2002</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>80</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FE3B6B-059D-4ACC-AECD-295DB57A9456}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3D625F-5982-4958-A0C9-5ACC898915E9}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="188">
   <si>
     <t>PerkID</t>
   </si>
@@ -840,7 +840,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 80 회복한다</t>
     </r>
@@ -883,6 +883,10 @@
   </si>
   <si>
     <t>Icons/Slash_Bracelet</t>
+  </si>
+  <si>
+    <t>Price</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -972,7 +976,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -995,12 +999,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1043,6 +1067,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1884,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1895,7 +1928,7 @@
     <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>145</v>
       </c>
@@ -1920,8 +1953,11 @@
       <c r="H1" s="13" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -1946,8 +1982,11 @@
       <c r="H2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -1972,8 +2011,11 @@
       <c r="H3" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>1003</v>
       </c>
@@ -1998,8 +2040,11 @@
       <c r="H4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="6">
         <v>1004</v>
       </c>
@@ -2024,8 +2069,11 @@
       <c r="H5" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>1005</v>
       </c>
@@ -2050,8 +2098,11 @@
       <c r="H6" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="6">
         <v>1006</v>
       </c>
@@ -2076,8 +2127,11 @@
       <c r="H7" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>1007</v>
       </c>
@@ -2101,6 +2155,9 @@
       </c>
       <c r="H8" t="s">
         <v>186</v>
+      </c>
+      <c r="I8" s="17">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2112,7 +2169,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6712144-EE6D-453D-A942-3F286BAEA58E}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -2123,7 +2180,7 @@
     <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="13" t="s">
         <v>168</v>
       </c>
@@ -2142,8 +2199,11 @@
       <c r="F1" s="13" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3">
         <v>2001</v>
       </c>
@@ -2162,8 +2222,11 @@
       <c r="F2" s="14" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>2002</v>
       </c>
@@ -2181,11 +2244,15 @@
       </c>
       <c r="F3" s="15" t="s">
         <v>179</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yoonj\Desktop\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3D625F-5982-4958-A0C9-5ACC898915E9}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03611FC-1FDE-4A19-AE52-479D13FE9097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="212">
   <si>
     <t>PerkID</t>
   </si>
@@ -856,36 +856,139 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Icons/Potion_Low</t>
+    <t>Price</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Icons/Potion_High</t>
+    <t>Icons/Items/Steel_Helmet</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Icons/Steel_Helmet</t>
-  </si>
-  <si>
-    <t>Icons/Leather_Armor</t>
-  </si>
-  <si>
-    <t>Icons/Swift_Boots</t>
-  </si>
-  <si>
-    <t>Icons/Power_Ring</t>
-  </si>
-  <si>
-    <t>Icons/Haste_Necklace</t>
-  </si>
-  <si>
-    <t>Icons/Guardian_Amulet</t>
-  </si>
-  <si>
-    <t>Icons/Slash_Bracelet</t>
-  </si>
-  <si>
-    <t>Price</t>
+    <t>Icons/Items/Leather_Armor</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Items/Swift_Boots</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Items/Power_Ring</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Items/Haste_Necklace</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Items/Guardian_Amulet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Items/Slash_Bracelet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Items/Potion_Low</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Items/Potion_High</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_MaxHP</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_SturdyBody</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_IronWall</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_Defense</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_Berserker</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_StormRush</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_Attack</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_DeadlyStrike</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_Executioner</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_Gale</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_MoveSpeed</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_CritDamage</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_SwordWave</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_FierceAssault</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_EarthShatter</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_SwordStorm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_Swiftness</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_ImmortalBarrier</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_AttackSpeed</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_CritChance</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_ChainExplosion</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_PiercingExplosion</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_ShatteringImpact</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Perks/Perk_CombatSense</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -893,7 +996,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -955,8 +1058,21 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -975,8 +1091,20 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1019,14 +1147,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1072,12 +1214,22 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1344,73 +1496,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80FDACC5-480A-45D9-990F-F547CEC76173}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13">
         <v>100</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>20</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>5</v>
       </c>
-      <c r="E2" s="14">
-        <v>2</v>
-      </c>
-      <c r="F2" s="14">
+      <c r="E2" s="13">
+        <v>2</v>
+      </c>
+      <c r="F2" s="13">
         <v>5</v>
       </c>
-      <c r="G2" s="14">
-        <v>0</v>
-      </c>
-      <c r="H2" s="14">
+      <c r="G2" s="13">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13">
         <v>5</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>150</v>
       </c>
     </row>
@@ -1423,52 +1575,52 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" customWidth="1"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>3001</v>
       </c>
-      <c r="C2" s="3">
-        <v>3</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>1001</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>3</v>
       </c>
     </row>
@@ -1482,45 +1634,45 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="4" width="11" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="3">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
         <v>200</v>
       </c>
     </row>
@@ -1534,63 +1686,63 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
-      <c r="D3" s="6">
-        <v>3</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
         <v>1</v>
       </c>
     </row>
@@ -1604,219 +1756,219 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>101</v>
       </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>102</v>
       </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6">
-        <v>2</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
         <v>5</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>103</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>201</v>
       </c>
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6">
-        <v>2</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
         <v>5</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>202</v>
       </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
         <v>5</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>203</v>
       </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6">
-        <v>3</v>
-      </c>
-      <c r="E7" s="6">
-        <v>2</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>2</v>
       </c>
     </row>
@@ -1830,81 +1982,81 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>101</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>1001</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>102</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>1001</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
         <v>201</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>1001</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>202</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>1001</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>100</v>
       </c>
     </row>
@@ -1918,245 +2070,245 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>187</v>
+      <c r="I1" s="15" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1001</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
         <v>10</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>149</v>
       </c>
       <c r="H2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2" s="16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="5">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>15</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" t="s">
         <v>180</v>
       </c>
-      <c r="I2" s="17">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="6">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
-      <c r="D3" s="6">
-        <v>3</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="I3" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>8</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>12</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="17">
         <v>15</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="H3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I3" s="18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="3">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="2">
         <v>4</v>
       </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>8</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I4" s="17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="6">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6">
-        <v>2</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6">
-        <v>8</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" t="s">
-        <v>183</v>
-      </c>
-      <c r="I5" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="3">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="3">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>10</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="H6" t="s">
-        <v>184</v>
-      </c>
-      <c r="I6" s="17">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="6">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="6">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6">
-        <v>3</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6">
-        <v>12</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="D8" s="2">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H8" t="s">
         <v>185</v>
       </c>
-      <c r="I7" s="18">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="3">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H8" t="s">
-        <v>186</v>
-      </c>
-      <c r="I8" s="17">
+      <c r="I8" s="16">
         <v>12</v>
       </c>
     </row>
@@ -2170,80 +2322,80 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6712144-EE6D-453D-A942-3F286BAEA58E}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>187</v>
+      <c r="G1" s="15" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>2001</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
         <v>30</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>178</v>
+      <c r="F2" s="13" t="s">
+        <v>186</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2002</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="6">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
         <v>80</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>179</v>
+      <c r="F3" s="14" t="s">
+        <v>187</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -2258,515 +2410,591 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="55" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="109.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+    <row r="1" spans="1:7" ht="15" customHeight="1">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1">
-      <c r="A2" s="3">
+      <c r="G1" s="18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="19">
         <v>1001</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="19">
+        <v>1</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1">
-      <c r="A3" s="6">
+      <c r="G2" s="20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="19">
         <v>1002</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="C3" s="19">
+        <v>1</v>
+      </c>
+      <c r="D3" s="19">
+        <v>0</v>
+      </c>
+      <c r="E3" s="19">
         <v>5</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1">
-      <c r="A4" s="3">
+      <c r="G3" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="19">
         <v>1003</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0</v>
+      </c>
+      <c r="E4" s="19">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="G4" s="20" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="19">
         <v>1004</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="C5" s="19">
+        <v>1</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0</v>
+      </c>
+      <c r="E5" s="19">
         <v>5</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="20" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="G5" s="20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="19">
         <v>1005</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="C6" s="19">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0</v>
+      </c>
+      <c r="E6" s="19">
         <v>5</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1">
-      <c r="A7" s="6">
+      <c r="G6" s="20" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A7" s="19">
         <v>1006</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="C7" s="19">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19">
         <v>5</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="3">
+      <c r="G7" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="19">
         <v>1007</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="C8" s="19">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19">
         <v>5</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1">
-      <c r="A9" s="6">
+      <c r="G8" s="20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="19">
         <v>2001</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="C9" s="19">
+        <v>2</v>
+      </c>
+      <c r="D9" s="19">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1">
-      <c r="A10" s="3">
+      <c r="G9" s="20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="19">
         <v>2002</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3">
-        <v>2</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="C10" s="19">
+        <v>2</v>
+      </c>
+      <c r="D10" s="19">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19">
+        <v>3</v>
+      </c>
+      <c r="F10" s="20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1">
-      <c r="A11" s="6">
+      <c r="G10" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="19">
         <v>2003</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="6">
-        <v>2</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>3</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="C11" s="19">
+        <v>2</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0</v>
+      </c>
+      <c r="E11" s="19">
+        <v>3</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="A12" s="3">
+      <c r="G11" s="20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="19">
         <v>2004</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="C12" s="19">
+        <v>2</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19">
+        <v>3</v>
+      </c>
+      <c r="F12" s="20" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" s="6">
+      <c r="G12" s="20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A13" s="19">
         <v>3001</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="6">
-        <v>3</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="C13" s="19">
+        <v>3</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0</v>
+      </c>
+      <c r="E13" s="19">
+        <v>2</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1">
-      <c r="A14" s="3">
+      <c r="G13" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A14" s="19">
         <v>3002</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="3">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="C14" s="19">
+        <v>3</v>
+      </c>
+      <c r="D14" s="19">
+        <v>0</v>
+      </c>
+      <c r="E14" s="19">
+        <v>2</v>
+      </c>
+      <c r="F14" s="20" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1">
-      <c r="A15" s="6">
+      <c r="G14" s="20" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A15" s="19">
         <v>3003</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="6">
-        <v>3</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>2</v>
-      </c>
-      <c r="F15" s="8" t="s">
+      <c r="C15" s="19">
+        <v>3</v>
+      </c>
+      <c r="D15" s="19">
+        <v>0</v>
+      </c>
+      <c r="E15" s="19">
+        <v>2</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1">
-      <c r="A16" s="3">
+      <c r="G15" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A16" s="19">
         <v>3004</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="3">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="C16" s="19">
+        <v>3</v>
+      </c>
+      <c r="D16" s="19">
+        <v>0</v>
+      </c>
+      <c r="E16" s="19">
+        <v>2</v>
+      </c>
+      <c r="F16" s="20" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1">
-      <c r="A17" s="6">
+      <c r="G16" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A17" s="19">
         <v>3101</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="6">
-        <v>3</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8" t="s">
+      <c r="C17" s="19">
+        <v>3</v>
+      </c>
+      <c r="D17" s="19">
+        <v>1</v>
+      </c>
+      <c r="E17" s="19">
+        <v>1</v>
+      </c>
+      <c r="F17" s="20" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1">
-      <c r="A18" s="3">
+      <c r="G17" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A18" s="19">
         <v>3201</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="3">
-        <v>3</v>
-      </c>
-      <c r="D18" s="3">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="C18" s="19">
+        <v>3</v>
+      </c>
+      <c r="D18" s="19">
+        <v>2</v>
+      </c>
+      <c r="E18" s="19">
+        <v>1</v>
+      </c>
+      <c r="F18" s="20" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1">
-      <c r="A19" s="6">
+      <c r="G18" s="20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A19" s="19">
         <v>3301</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="6">
-        <v>3</v>
-      </c>
-      <c r="D19" s="6">
-        <v>3</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8" t="s">
+      <c r="C19" s="19">
+        <v>3</v>
+      </c>
+      <c r="D19" s="19">
+        <v>3</v>
+      </c>
+      <c r="E19" s="19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1">
-      <c r="A20" s="3">
+      <c r="G19" s="20" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="19">
         <v>4001</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="19">
         <v>4</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="5" t="s">
+      <c r="D20" s="19">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19">
+        <v>1</v>
+      </c>
+      <c r="F20" s="20" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1">
-      <c r="A21" s="6">
+      <c r="G20" s="20" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A21" s="19">
         <v>4002</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="19">
         <v>4</v>
       </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8" t="s">
+      <c r="D21" s="19">
+        <v>0</v>
+      </c>
+      <c r="E21" s="19">
+        <v>1</v>
+      </c>
+      <c r="F21" s="20" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1">
-      <c r="A22" s="3">
+      <c r="G21" s="20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A22" s="19">
         <v>4003</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="19">
         <v>4</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="D22" s="19">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19">
+        <v>1</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1">
-      <c r="A23" s="6">
+      <c r="G22" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="19">
         <v>4101</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="19">
         <v>4</v>
       </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1</v>
-      </c>
-      <c r="F23" s="8" t="s">
+      <c r="D23" s="19">
+        <v>1</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1</v>
+      </c>
+      <c r="F23" s="20" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1">
-      <c r="A24" s="3">
+      <c r="G23" s="20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A24" s="19">
         <v>4201</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="19">
         <v>4</v>
       </c>
-      <c r="D24" s="3">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5" t="s">
+      <c r="D24" s="19">
+        <v>2</v>
+      </c>
+      <c r="E24" s="19">
+        <v>1</v>
+      </c>
+      <c r="F24" s="20" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1">
-      <c r="A25" s="6">
+      <c r="G24" s="20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="21" customFormat="1" ht="15" customHeight="1">
+      <c r="A25" s="19">
         <v>4301</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="19">
         <v>4</v>
       </c>
-      <c r="D25" s="6">
-        <v>3</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1</v>
-      </c>
-      <c r="F25" s="8" t="s">
+      <c r="D25" s="19">
+        <v>3</v>
+      </c>
+      <c r="E25" s="19">
+        <v>1</v>
+      </c>
+      <c r="F25" s="20" t="s">
         <v>53</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2779,674 +3007,674 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>1001</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>1002</v>
       </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
         <v>1003</v>
       </c>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>1004</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>4</v>
       </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>1005</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>1006</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>6</v>
       </c>
-      <c r="D7" s="6">
-        <v>2</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>1007</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>2001</v>
       </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>2001</v>
       </c>
-      <c r="C10" s="3">
-        <v>3</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>2002</v>
       </c>
-      <c r="C11" s="6">
-        <v>2</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>2002</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>6</v>
       </c>
-      <c r="D12" s="3">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>2003</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>4</v>
       </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>2003</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>5</v>
       </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>2004</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>6</v>
       </c>
-      <c r="D15" s="6">
-        <v>2</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="D15" s="5">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>2004</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>7</v>
       </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>3001</v>
       </c>
-      <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>3001</v>
       </c>
-      <c r="C18" s="3">
-        <v>3</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>3002</v>
       </c>
-      <c r="C19" s="6">
-        <v>2</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="C19" s="5">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="2">
         <v>3002</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>6</v>
       </c>
-      <c r="D20" s="3">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>3003</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>4</v>
       </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <v>3003</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>5</v>
       </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>3004</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>6</v>
       </c>
-      <c r="D23" s="6">
-        <v>2</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="D23" s="5">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <v>3004</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>7</v>
       </c>
-      <c r="D24" s="3">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>4001</v>
       </c>
-      <c r="C25" s="6">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6">
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
         <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <v>4001</v>
       </c>
-      <c r="C26" s="3">
-        <v>3</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
         <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>4001</v>
       </c>
-      <c r="C27" s="6">
-        <v>2</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6">
+      <c r="C27" s="5">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
         <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>4002</v>
       </c>
-      <c r="C28" s="3">
-        <v>2</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="C28" s="2">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
         <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>4002</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>6</v>
       </c>
-      <c r="D29" s="6">
-        <v>2</v>
-      </c>
-      <c r="E29" s="6">
+      <c r="D29" s="5">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>4002</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="2">
         <v>7</v>
       </c>
-      <c r="D30" s="3">
-        <v>2</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2">
         <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
-      <c r="A31" s="6">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>4003</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>4</v>
       </c>
-      <c r="D31" s="6">
-        <v>1</v>
-      </c>
-      <c r="E31" s="6">
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>4003</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>5</v>
       </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>4003</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>6</v>
       </c>
-      <c r="D33" s="6">
-        <v>2</v>
-      </c>
-      <c r="E33" s="6">
+      <c r="D33" s="5">
+        <v>2</v>
+      </c>
+      <c r="E33" s="5">
         <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="2">
         <v>4101</v>
       </c>
-      <c r="C34" s="3">
-        <v>2</v>
-      </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3">
+      <c r="C34" s="2">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1">
-      <c r="A35" s="6">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>4101</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>6</v>
       </c>
-      <c r="D35" s="6">
-        <v>2</v>
-      </c>
-      <c r="E35" s="6">
+      <c r="D35" s="5">
+        <v>2</v>
+      </c>
+      <c r="E35" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1">
-      <c r="A36" s="3">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="2">
         <v>4201</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="2">
         <v>4</v>
       </c>
-      <c r="D36" s="3">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3">
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="5">
         <v>4201</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>5</v>
       </c>
-      <c r="D37" s="6">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6">
+      <c r="D37" s="5">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="2">
         <v>4301</v>
       </c>
-      <c r="C38" s="3">
-        <v>2</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3">
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1">
-      <c r="A39" s="6">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="5">
         <v>4301</v>
       </c>
-      <c r="C39" s="6">
-        <v>3</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1</v>
-      </c>
-      <c r="E39" s="6">
+      <c r="C39" s="5">
+        <v>3</v>
+      </c>
+      <c r="D39" s="5">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
         <v>23</v>
       </c>
     </row>
@@ -3460,173 +3688,173 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>3101</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
         <v>40</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>3201</v>
       </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
         <v>25</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>30</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>1.5</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
         <v>3301</v>
       </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
         <v>25</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>30</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>1.5</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>4101</v>
       </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
         <v>60</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4201</v>
       </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
         <v>100</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>50</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>2.5</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>4301</v>
       </c>
-      <c r="C7" s="6">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
         <v>100</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>50</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>2.5</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>2</v>
       </c>
     </row>
@@ -3640,238 +3868,238 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="3" width="12" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>100</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>100</v>
       </c>
-      <c r="H2" s="3">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
         <v>0.7</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>220</v>
       </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>3</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>100</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>12</v>
       </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.7</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6">
-        <v>2</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>180</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>14</v>
       </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
         <v>5</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>100</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>1.8</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>70</v>
       </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
         <v>0.7</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="5">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>250</v>
       </c>
-      <c r="F7" s="6">
-        <v>3</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="F7" s="5">
+        <v>3</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>2.5</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
         <v>8</v>
       </c>
     </row>
@@ -3885,163 +4113,163 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
         <v>-8</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
         <v>-10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
         <v>4</v>
       </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="B7" s="5">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="2">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
         <v>-12</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
-        <v>3</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="5">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5">
         <v>5</v>
       </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
         <v>-30</v>
       </c>
     </row>
@@ -4055,211 +4283,211 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1" customWidth="1"/>
-    <col min="13" max="13" width="22" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="1" customWidth="1"/>
-    <col min="16" max="17" width="14" style="1" customWidth="1"/>
-    <col min="18" max="18" width="15" style="1" customWidth="1"/>
-    <col min="19" max="20" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1001</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
         <v>57</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>10</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="3">
-        <v>2</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="G2" s="2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2">
         <v>5</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>8</v>
       </c>
-      <c r="J2" s="3">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3">
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
         <v>5</v>
       </c>
-      <c r="L2" s="3">
-        <v>2</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="L2" s="2">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O2" s="3">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3">
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>3001</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="6">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
         <v>800</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>25</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>15</v>
       </c>
-      <c r="G3" s="6">
-        <v>3</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5">
         <v>10</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>14</v>
       </c>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6">
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
         <v>100</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>50</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="5">
         <v>66</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Q3" s="6">
-        <v>1</v>
-      </c>
-      <c r="R3" s="6">
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
         <v>33</v>
       </c>
-      <c r="S3" s="6">
+      <c r="S3" s="5">
         <v>1.3</v>
       </c>
-      <c r="T3" s="6">
+      <c r="T3" s="5">
         <v>1.2</v>
       </c>
     </row>
@@ -4273,247 +4501,247 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>1001</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
         <v>100</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>1.2</v>
       </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3">
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
         <v>1.2</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>3001</v>
       </c>
-      <c r="C3" s="6">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
         <v>100</v>
       </c>
-      <c r="H3" s="6">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>1.5</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>1.5</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
         <v>3001</v>
       </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
         <v>180</v>
       </c>
-      <c r="H4" s="3">
-        <v>3</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
         <v>2.5</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>6</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>3001</v>
       </c>
-      <c r="C5" s="6">
-        <v>2</v>
-      </c>
-      <c r="D5" s="6">
-        <v>2</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="6">
-        <v>2</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5">
         <v>60</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>6</v>
       </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
         <v>10</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>3001</v>
       </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3">
-        <v>3</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="3">
-        <v>3</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
         <v>15</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4527,67 +4755,67 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>3001</v>
       </c>
-      <c r="C2" s="3">
-        <v>2</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>90</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>0.7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>117</v>
       </c>
     </row>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yoonj\Desktop\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03611FC-1FDE-4A19-AE52-479D13FE9097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDC40AE-6786-449B-BFB3-4DD18F9DC893}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -1496,14 +1496,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80FDACC5-480A-45D9-990F-F547CEC76173}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="9" width="11" customWidth="1"/>
   </cols>
@@ -1575,7 +1575,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
@@ -1634,7 +1634,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1686,7 +1686,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1756,7 +1756,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1982,7 +1982,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -2070,14 +2070,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2322,14 +2322,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6712144-EE6D-453D-A942-3F286BAEA58E}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2411,15 +2411,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="109.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="131.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
@@ -3007,7 +3007,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -3688,7 +3688,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -3868,7 +3868,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -4113,7 +4113,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="4" width="12" customWidth="1"/>
@@ -4283,7 +4283,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4501,7 +4501,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -4755,7 +4755,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDC40AE-6786-449B-BFB3-4DD18F9DC893}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9859582A-238B-4F7B-86E5-AE8859C44D47}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2625" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -1167,7 +1167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1230,6 +1230,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1981,7 +1984,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2033,30 +2036,44 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22">
+        <v>103</v>
+      </c>
+      <c r="C4" s="22">
+        <v>1001</v>
+      </c>
+      <c r="D4" s="22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
         <v>201</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C5" s="2">
         <v>1001</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D5" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="6" spans="1:4">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
         <v>202</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C6" s="5">
         <v>1001</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D6" s="5">
         <v>100</v>
       </c>
     </row>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9859582A-238B-4F7B-86E5-AE8859C44D47}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B034005C-7217-47D6-9C10-87F1FB3FBB4A}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2625" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B034005C-7217-47D6-9C10-87F1FB3FBB4A}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D13AE8D-4510-4755-A8AD-6A6FC2ABE803}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2625" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2625" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -2043,7 +2043,7 @@
         <v>103</v>
       </c>
       <c r="C4" s="22">
-        <v>1001</v>
+        <v>3001</v>
       </c>
       <c r="D4" s="22">
         <v>100</v>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D13AE8D-4510-4755-A8AD-6A6FC2ABE803}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F9719E-A370-4E37-96F2-8956D1B27110}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2625" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
@@ -1987,7 +1987,7 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>50</v>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F9719E-A370-4E37-96F2-8956D1B27110}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E0CC54-A8F0-4EF9-9C07-1404BF005D4C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4308,13 +4308,13 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="17" width="14" customWidth="1"/>
@@ -4469,7 +4469,7 @@
         <v>3</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>14</v>

--- a/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
+++ b/Tools/ExcelDataParser/GameDataTableConverter/Table/GameDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dclass\Desktop\yj\portfolio\endless-day\Tools\ExcelDataParser\GameDataTableConverter\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E0CC54-A8F0-4EF9-9C07-1404BF005D4C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D942F4E-8CF1-40C9-BA95-C8BC3135B023}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerBaseStatTable" sheetId="15" r:id="rId1"/>
